--- a/artfynd/A 47929-2025 artfynd.xlsx
+++ b/artfynd/A 47929-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184838</v>
       </c>
       <c r="B2" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130184836</v>
       </c>
       <c r="B3" t="n">
-        <v>79095</v>
+        <v>79180</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47929-2025 artfynd.xlsx
+++ b/artfynd/A 47929-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184838</v>
       </c>
       <c r="B2" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130184836</v>
       </c>
       <c r="B3" t="n">
-        <v>79180</v>
+        <v>79183</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47929-2025 artfynd.xlsx
+++ b/artfynd/A 47929-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184838</v>
       </c>
       <c r="B2" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130184836</v>
       </c>
       <c r="B3" t="n">
-        <v>79183</v>
+        <v>79209</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47929-2025 artfynd.xlsx
+++ b/artfynd/A 47929-2025 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>130184838</v>
       </c>
       <c r="B2" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -790,7 +790,7 @@
         <v>130184836</v>
       </c>
       <c r="B3" t="n">
-        <v>79209</v>
+        <v>79211</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 47929-2025 artfynd.xlsx
+++ b/artfynd/A 47929-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>130184838</v>
+        <v>130184836</v>
       </c>
       <c r="B2" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>817348</v>
+        <v>817315</v>
       </c>
       <c r="R2" t="n">
-        <v>7329243</v>
+        <v>7329267</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -787,14 +787,14 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>130184836</v>
+        <v>130184838</v>
       </c>
       <c r="B3" t="n">
-        <v>79211</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -822,10 +822,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>817315</v>
+        <v>817348</v>
       </c>
       <c r="R3" t="n">
-        <v>7329267</v>
+        <v>7329243</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -896,6 +896,230 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>130184840</v>
+      </c>
+      <c r="B4" t="n">
+        <v>80336</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>6456</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Skinnlav</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Leptogium saturninum</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Dicks.) Nyl.</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Haparanda-Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>817280</v>
+      </c>
+      <c r="R4" t="n">
+        <v>7329268</v>
+      </c>
+      <c r="S4" t="n">
+        <v>10</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>130184841</v>
+      </c>
+      <c r="B5" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Haparanda-Boden, Nb</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>817278</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7329273</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Boden</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Norrbotten</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Överluleå</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-09-01</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>NVI (C250260) Calluna AB</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jonas Mattsson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Julia Svensson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
